--- a/RoleFinder/job profiles.xlsx
+++ b/RoleFinder/job profiles.xlsx
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="154">
   <si>
     <t xml:space="preserve">מחלקה</t>
   </si>
@@ -729,7 +729,7 @@
     <t xml:space="preserve">ניסיון באינטגרציה </t>
   </si>
   <si>
-    <t xml:space="preserve">גר/ה רחוק בכרמיאל או נהריה </t>
+    <t xml:space="preserve">גר/ה רחוק בכרמיאל/נהריה </t>
   </si>
   <si>
     <t xml:space="preserve">רגישות לחומרים </t>
@@ -849,7 +849,7 @@
     <t xml:space="preserve">25-50</t>
   </si>
   <si>
-    <t xml:space="preserve">בזריזה </t>
+    <t xml:space="preserve">בתנועה </t>
   </si>
   <si>
     <t xml:space="preserve">38-40</t>
@@ -1111,6 +1111,9 @@
   </si>
   <si>
     <t xml:space="preserve">עם מיכרוסקופ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בתנועה</t>
   </si>
   <si>
     <t xml:space="preserve">20-35 </t>
@@ -10698,7 +10701,7 @@
       </c>
       <c r="D6" s="102"/>
       <c r="E6" s="95" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="F6" s="95" t="s">
         <v>95</v>
@@ -10786,7 +10789,7 @@
     </row>
     <row r="9" customFormat="false" ht="32" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="105" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" s="100" t="s">
         <v>94</v>

--- a/RoleFinder/job profiles.xlsx
+++ b/RoleFinder/job profiles.xlsx
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="164">
   <si>
     <t xml:space="preserve">מחלקה</t>
   </si>
@@ -696,394 +696,412 @@
     <t xml:space="preserve">הנדסאי אלקטרוניקה</t>
   </si>
   <si>
+    <t xml:space="preserve">הרכבות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אינטגרציה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הלחמות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בקרת איכות אלקטרוניקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רישיון נהיגה  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפעיל/ת מכונה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ידע במחשב ותוכנות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כתב יד ברור </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מוטוריקה עדינה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">גר/ה רחוק בכרמיאל/נהריה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רגישות לחומרים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">חיווט </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ארד דליה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלחימה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נקבה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבוע בוקר+2-3 ש"נ בשבוע </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לטווח זמן מעל שנה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בישיבה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בסיסית </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אין בכלל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לא </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אין</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרכיב </t>
+  </si>
+  <si>
+    <t xml:space="preserve">לא משנה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אין </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מריץ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש חומר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">זכר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אורז </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biosense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC TU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שליטה טובה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן, עם לופה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן, בהלחמות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבוע בוקר/שבוע ערב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בעמידה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אינטגרטור </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן, במכניקה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלחימה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן, עם מיקרוסקופ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בתנועה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">38-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בהליכה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia  NPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבוע בוקר/לילה 12/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מועדפת </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia  Black Mamba </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia HCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia SW </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia Juliet  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nvidia SFG  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפעיל X-RAY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">X-ray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ציפוי ידני </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ציפוי ספריי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חווט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפעיל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבוע בוקר (ש"נ 4 פעמים בשבוע) - שבוע לילה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שפת אם </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מבקרתSMT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כן, בהלחמות SMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation AST </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפעיל מכונה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rework BGA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ייצור משלים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרכיב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלחים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כללי 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלחים ללא ניסיון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">כללי 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קורס הלחמות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלחימה ללא ניסיון </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן קבלה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסנאי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">חודש עם שבוע אחד של לילות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן ביקורת קבלה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן קבלה (פיזית) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן קאנבן Nvidia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן תוצ"ג </t>
+  </si>
+  <si>
+    <t xml:space="preserve">שבוע בוקר+5 ש"נ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן מידוף קבד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן SMT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מחסן מידוף קל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הנדסת NVIDIA - טכנאי עמדות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי עמדות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נתונים דמוגרפיים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניסיון בבקרת איכות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">סוג שעות עבודה </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> טווח זמן לעבוד </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אופי של עבודה </t>
+  </si>
+  <si>
+    <t xml:space="preserve">זמינות להרים משכלים עד 15 קילו </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הנדסאי אלקטרוניקה? </t>
+  </si>
+  <si>
     <t xml:space="preserve">ניסיון בהרכבות </t>
   </si>
   <si>
+    <t xml:space="preserve">ניסיון באינטגרציה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניסיון בביקרת איכות בתחום אלקטרוניקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניסיון עם כלים </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניסיון בהלחמות </t>
+  </si>
+  <si>
     <t xml:space="preserve">ניסיון באינטגרציה </t>
   </si>
   <si>
-    <t xml:space="preserve">ניסיון בהלחמות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון בבקרת איכות אלקטרוניקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון עם כלים </t>
-  </si>
-  <si>
     <t xml:space="preserve">ניסיון במחסן </t>
   </si>
   <si>
-    <t xml:space="preserve">רישיון נהיגה  </t>
+    <t xml:space="preserve">רישיון מלגזה </t>
   </si>
   <si>
     <t xml:space="preserve">ניסיון כמפעיל/ת מכונה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ידע במחשב ותוכנות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כתב יד ברור </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מוטוריקה עדינה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">גר/ה רחוק בכרמיאל/נהריה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">רגישות לחומרים </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון בחיווט </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ארד דליה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מלחימה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">נקבה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שבוע בוקר+2-3 ש"נ בשבוע </t>
-  </si>
-  <si>
-    <t xml:space="preserve">לטווח זמן מעל שנה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">בישיבה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">בסיסית </t>
-  </si>
-  <si>
-    <t xml:space="preserve">אין בכלל </t>
-  </si>
-  <si>
-    <t xml:space="preserve">לא </t>
-  </si>
-  <si>
-    <t xml:space="preserve">לא</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אין</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרכיב </t>
-  </si>
-  <si>
-    <t xml:space="preserve">לא משנה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן </t>
-  </si>
-  <si>
-    <t xml:space="preserve">אין </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מריץ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש חומר </t>
-  </si>
-  <si>
-    <t xml:space="preserve">זכר </t>
-  </si>
-  <si>
-    <t xml:space="preserve">אורז </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biosense </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QC TU </t>
-  </si>
-  <si>
-    <t xml:space="preserve">שליטה טובה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן, עם לופה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן, בהלחמות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">שבוע בוקר/שבוע ערב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בעמידה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">אינטגרטור </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן, במכניקה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מלחימה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן, עם מיקרוסקופ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בתנועה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">38-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בהליכה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia  NPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שבוע בוקר/לילה 12/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מועדפת </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia  Black Mamba </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia HCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia SW </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia Juliet  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia SFG  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מפעיל X-RAY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">X-ray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ציפוי ידני </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ציפוי ספריי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חווט</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מפעיל </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שבוע בוקר (ש"נ 4 פעמים בשבוע) - שבוע לילה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">שפת אם </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מבקרתSMT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כן, בהלחמות SMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation AST </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מפעיל מכונה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rework BGA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ייצור משלים </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרכיב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מלחים </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כללי 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מלחים ללא ניסיון </t>
-  </si>
-  <si>
-    <t xml:space="preserve">כללי 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">קורס הלחמות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מלחימה ללא ניסיון </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן קבלה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסנאי </t>
-  </si>
-  <si>
-    <t xml:space="preserve">חודש עם שבוע אחד של לילות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן ביקורת קבלה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן קבלה (פיזית) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן קאנבן Nvidia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן תוצ"ג </t>
-  </si>
-  <si>
-    <t xml:space="preserve">שבוע בוקר+5 ש"נ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן מידוף קבד </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-40 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן SMT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">מחסן מידוף קל </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הנדסת NVIDIA - טכנאי עמדות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי עמדות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">נתונים דמוגרפיים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון בבקרת איכות </t>
-  </si>
-  <si>
-    <t xml:space="preserve">סוג שעות עבודה </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> טווח זמן לעבוד </t>
-  </si>
-  <si>
-    <t xml:space="preserve">אופי של עבודה </t>
-  </si>
-  <si>
-    <t xml:space="preserve">זמינות להרים משכלים עד 15 קילו </t>
-  </si>
-  <si>
-    <t xml:space="preserve">הנדסאי אלקטרוניקה? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון באינטגרציה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ניסיון בביקרת איכות בתחום אלקטרוניקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">רישיון מלגזה </t>
   </si>
   <si>
     <t xml:space="preserve">ידע במחש ותוכנות </t>
@@ -10178,55 +10196,55 @@
         <v>139</v>
       </c>
       <c r="L2" s="86" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="M2" s="87" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N2" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="O2" s="89" t="s">
+        <v>143</v>
+      </c>
+      <c r="P2" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q2" s="86" t="s">
+        <v>145</v>
+      </c>
+      <c r="R2" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="S2" s="86" t="s">
+        <v>147</v>
+      </c>
+      <c r="T2" s="86" t="s">
+        <v>148</v>
+      </c>
+      <c r="U2" s="86" t="s">
+        <v>149</v>
+      </c>
+      <c r="V2" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="W2" s="86" t="s">
+        <v>151</v>
+      </c>
+      <c r="X2" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="O2" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="90" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="86" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="86" t="s">
-        <v>142</v>
-      </c>
-      <c r="T2" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="V2" s="86" t="s">
-        <v>144</v>
-      </c>
-      <c r="W2" s="86" t="s">
-        <v>145</v>
-      </c>
-      <c r="X2" s="86" t="s">
-        <v>140</v>
-      </c>
       <c r="Y2" s="91" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Z2" s="92" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="AA2" s="92" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AB2" s="92" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10237,7 +10255,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="93" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D3" s="93" t="s">
         <v>77</v>
@@ -10324,7 +10342,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="93" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E4" s="95" t="s">
         <v>67</v>
@@ -10357,7 +10375,7 @@
         <v>58</v>
       </c>
       <c r="O4" s="96" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="P4" s="99" t="s">
         <v>36</v>
@@ -10372,7 +10390,7 @@
         <v>36</v>
       </c>
       <c r="T4" s="96" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="U4" s="93" t="s">
         <v>34</v>
@@ -10431,7 +10449,7 @@
         <v>53</v>
       </c>
       <c r="O5" s="96" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P5" s="99" t="s">
         <v>52</v>
@@ -10458,7 +10476,7 @@
       </c>
       <c r="D6" s="102"/>
       <c r="E6" s="95" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F6" s="95" t="s">
         <v>97</v>
@@ -10482,7 +10500,7 @@
       <c r="R6" s="93"/>
       <c r="S6" s="93"/>
       <c r="T6" s="93" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="U6" s="93"/>
       <c r="V6" s="93"/>
@@ -10548,7 +10566,7 @@
     </row>
     <row r="9" customFormat="false" ht="32" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="105" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C9" s="100" t="s">
         <v>96</v>

--- a/RoleFinder/job profiles.xlsx
+++ b/RoleFinder/job profiles.xlsx
@@ -675,7 +675,7 @@
     <t xml:space="preserve">טווח</t>
   </si>
   <si>
-    <t xml:space="preserve">אופי העבודה</t>
+    <t xml:space="preserve">אופי העבודה M</t>
   </si>
   <si>
     <t xml:space="preserve">אנגלית </t>
